--- a/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68AACA8-4DF1-4968-93AA-857531E039EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F3D090-8815-40E0-BB4C-E4E71C14FF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3264" yWindow="2280" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Cantidad de víctimas (enero - diciembre 2020)</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Cantidad de víctimas (enero - diciembre 2025)</t>
+  </si>
+  <si>
+    <t>Cantidad de víctimas (enero - abril 2026)</t>
   </si>
 </sst>
 </file>
@@ -116,10 +119,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -335,41 +347,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="39.09765625" customWidth="1"/>
-    <col min="3" max="3" width="41.3984375" customWidth="1"/>
-    <col min="4" max="6" width="39.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.796875" customWidth="1"/>
-    <col min="8" max="26" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="22.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="21.796875" customWidth="1"/>
+    <col min="5" max="6" width="22.3984375" customWidth="1"/>
+    <col min="7" max="7" width="21.296875" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="H1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -391,8 +408,11 @@
       <c r="G2">
         <v>1540</v>
       </c>
+      <c r="H2">
+        <v>335</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -414,8 +434,11 @@
       <c r="G3">
         <v>103</v>
       </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -437,8 +460,11 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -460,18 +486,21 @@
       <c r="G5">
         <v>82</v>
       </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
